--- a/output/idea.xlsx
+++ b/output/idea.xlsx
@@ -463,32 +463,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Rahasia Cepat Hafal Perkalian!</t>
+          <t>AI Bisa Bikin Musik? 🤖🎵 Komposer Masa Depan?! #AIMusic #MusikAI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mau jago matematika? Video ini bongkar trik cepat menghafal perkalian! Gak perlu pusing lagi, dijamin langsung bisa. Triknya mudah dan seru! Yuk, tonton sampai habis dan buktikan sendiri! #trikmatematika #belajarsambilbermain #perkalianmudah #matematikaseru #tipsanak</t>
+          <t>Bayangin AI bisa bikin musik sendiri! Di video ini, gue bakal nunjukkin gimana AI bisa jadi komposer dadakan. Kita coba bikin lagu dari nol pakai AI, dengerin hasilnya, dan diskusi apakah AI bisa gantiin musisi manusia. 🤔
+#AI #ArtificialIntelligence #MusikGenerator #LaguAI #AIvsMusisi #TeknologiMusik #InovasiMusik #KreasiMusik</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Anak-anak usia 7-12 tahun</t>
+          <t>18-30 tahun</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>['Mempelajari cara cepat menghafal perkalian.', 'Membuat matematika menjadi lebih menyenangkan.', 'Meningkatkan kemampuan matematika dasar.']</t>
+          <t>['Memahami kemampuan AI dalam menciptakan musik.', 'Mendapatkan informasi tentang tools AI yang bisa digunakan untuk membuat musik.', 'Memahami potensi dan batasan AI dalam industri musik.']</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>#trikmatematika #belajarmatematika #perkaliancepat #matematikaseru #tipsanak #fyp #viral #kids #education</t>
+          <t>#AI #ArtificialIntelligence #MusikGenerator #LaguAI #AIvsMusisi #TeknologiMusik #InovasiMusik #KreasiMusik #fyp #viral #trending #musik</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anak-anak sering kesulitan menghafal perkalian. Video ini menawarkan solusi dengan trik yang mudah diingat, dikemas dengan visual yang menarik sehingga proses belajar lebih menyenangkan. Hashtag populer ditambahkan untuk meningkatkan kemungkinan video muncul di FYP.</t>
+          <t>Musik adalah bagian penting dari kehidupan sehari-hari. Menunjukkan bagaimana AI dapat menciptakan musik akan menarik minat audiens, terutama yang tertarik dengan musik dan teknologi. Ada unsur debat (AI vs Musisi) yang bisa memicu komentar dan interaksi.</t>
         </is>
       </c>
     </row>

--- a/output/idea.xlsx
+++ b/output/idea.xlsx
@@ -463,33 +463,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Bisa Bikin Musik? 🤖🎵 Komposer Masa Depan?! #AIMusic #MusikAI</t>
+          <t>Misteri Angka 11:11 - Kode Alam Semesta?</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bayangin AI bisa bikin musik sendiri! Di video ini, gue bakal nunjukkin gimana AI bisa jadi komposer dadakan. Kita coba bikin lagu dari nol pakai AI, dengerin hasilnya, dan diskusi apakah AI bisa gantiin musisi manusia. 🤔
-#AI #ArtificialIntelligence #MusikGenerator #LaguAI #AIvsMusisi #TeknologiMusik #InovasiMusik #KreasiMusik</t>
+          <t>Pernah lihat jam 11:11 terus-menerus? Banyak yang percaya itu bukan kebetulan! Video ini membahas teori di balik fenomena angka 11:11, mulai dari pesan malaikat, aktivasi spiritual, hingga sinkronisitas alam semesta. Apakah ini tanda dari alam semesta untukmu? Temukan jawabannya! #1111 #AngkaMalaikat #Spiritualitas #Konspirasi #MisteriAlamSemesta #TikTokIndonesia #YouTubeShortsIndonesia</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18-30 tahun</t>
+          <t>Semua umur</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>['Memahami kemampuan AI dalam menciptakan musik.', 'Mendapatkan informasi tentang tools AI yang bisa digunakan untuk membuat musik.', 'Memahami potensi dan batasan AI dalam industri musik.']</t>
+          <t>['Memahami fenomena angka 11:11 dari berbagai sudut pandang.', 'Mengetahui potensi makna spiritual di balik angka tersebut.', 'Terinspirasi untuk lebih memperhatikan sinkronisitas dalam hidup.']</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>#AI #ArtificialIntelligence #MusikGenerator #LaguAI #AIvsMusisi #TeknologiMusik #InovasiMusik #KreasiMusik #fyp #viral #trending #musik</t>
+          <t>#1111 #AngkaMalaikat #Spiritualitas #Konspirasi #MisteriAlamSemesta #TikTokIndonesia #YouTubeShortsIndonesia #foryou #fyp #viral</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Musik adalah bagian penting dari kehidupan sehari-hari. Menunjukkan bagaimana AI dapat menciptakan musik akan menarik minat audiens, terutama yang tertarik dengan musik dan teknologi. Ada unsur debat (AI vs Musisi) yang bisa memicu komentar dan interaksi.</t>
+          <t>Banyak orang tertarik dengan fenomena angka 11:11, menjadikannya topik yang menarik dan mudah viral. Judul yang membangkitkan rasa ingin tahu akan mendorong orang untuk menonton.</t>
         </is>
       </c>
     </row>
